--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD1246C-1F2A-4FB4-B657-68B3E5F9BB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0511E8-A989-4C3E-AEA2-77109A6659F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5730" windowWidth="44100" windowHeight="14560" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="-3020" yWindow="3730" windowWidth="41280" windowHeight="14560" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -77,126 +77,166 @@
     <t>SortOrder</t>
   </si>
   <si>
+    <t>魔法士</t>
+  </si>
+  <si>
+    <t>魔导士</t>
+  </si>
+  <si>
+    <t>黑魔法师</t>
+  </si>
+  <si>
+    <t>公主</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>角色/职业ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形态线 基础=1 爆发=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>觉醒所需等级(仅基础线用；爆发线靠宝石解锁，填0)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>同一形态线内的排序(爆发形态左右翻的顺序)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>形态名</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中文原文</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>IconKey</t>
   </si>
   <si>
-    <t>ArtKey</t>
+    <t>头像-Addressable完整路径</t>
   </si>
   <si>
     <t>SpineKey</t>
   </si>
   <si>
-    <t>IdleAnimation</t>
-  </si>
-  <si>
-    <t>VideoKey</t>
-  </si>
-  <si>
-    <t>魔法士</t>
+    <t>战斗Spine-Addressable完整路径</t>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Texture2D/Unit/icon_unit_106011.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Skeleton/Game/106011_SkeletonData.asset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/Unit/icon_unit_106031.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/Unit/icon_unit_106061.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/202/Texture2D/Unit/icon_unit_180611.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>门槛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Texture2D/CharacterFull/bsm_chara_full_106001_l.png</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Skeleton/Game/106011_SkeletonData.asset</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>魔导士</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/Unit/icon_unit_106031.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Video/106031.asset</t>
-  </si>
-  <si>
-    <t>黑魔法师</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/Unit/icon_unit_106061.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Video/106061.asset</t>
-  </si>
-  <si>
-    <t>公主</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/202/Texture2D/Unit/icon_unit_180611.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/202/Video/180611.asset</t>
-  </si>
-  <si>
-    <t>暗黑圣灵</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/202/Texture2D/Unit/icon_unit_180631.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/202/Video/180631.asset</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>角色/职业ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>形态ID(同一角色内唯一，约定 基础线1~99 / 爆发线101起)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>形态线 基础=1 爆发=2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>星级门槛。基础线:达到该星级即切到这一形态(1基础/3一觉/6二觉)；爆发线:填6只表示它是6星形态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>觉醒所需等级(仅基础线用；爆发线靠宝石解锁，填0)</t>
+    <t>StillUnitPrefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtImage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>c</t>
-  </si>
-  <si>
-    <t>形态名-中文原文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同一形态线内的排序(爆发形态左右翻的顺序)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>头像-Addressable完整路径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘-Addressable完整路径(只有基础形态填)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗Spine-Addressable完整路径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待机动画名(Spine里的动画名)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>视频-AVPro MediaReference完整路径(觉醒/爆发形态填)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/StillUnit/StillUnit106031Preview.prefab</t>
+  </si>
+  <si>
+    <t>预览图预制体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立绘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/201/Prefab/StillUnit/StillUnit106031Preview.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/202/Prefab/StillUnit202.prefab</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans SC"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>形态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ID</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -204,7 +244,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,6 +255,26 @@
     <font>
       <sz val="9"/>
       <name val="Consolas"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans SC"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -241,12 +301,39 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -582,361 +669,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA7DFF8-FE44-4B9E-AF79-499E40D6D221}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.08203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16" style="2" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.9140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="40" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="31.6640625" style="9" customWidth="1"/>
+    <col min="12" max="12" width="36.75" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>10</v>
+      <c r="K2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="1" t="s">
+    </row>
+    <row r="7" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="1" t="s">
+    </row>
+    <row r="8" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>101</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="9" t="s">
         <v>43</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>60</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>101</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>102</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0511E8-A989-4C3E-AEA2-77109A6659F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2CA86A-DAC7-48CD-A856-515C3AA9C5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3020" yWindow="3730" windowWidth="41280" windowHeight="14560" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="-12220" yWindow="3600" windowWidth="47520" windowHeight="15840" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -238,6 +238,46 @@
       <t>ID</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圣职者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神赐者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大天使</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Texture2D/Unit/icon_unit_100211.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/101/Texture2D/Unit/icon_unit_100231.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/101/Texture2D/Unit/icon_unit_100261.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Skeleton/100211_SkeletonData.asset</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Texture2D/CharacterFull/bsm_chara_full_102001_l.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/101/Prefab/StillUnit/StillUnit_101.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/101/Prefab/StillUnit/StillUnit_102.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/102/Texture2D/Unit/icon_unit_180211.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/102/Prefab/StillUnit/StillUnit_180231.prefab</t>
   </si>
 </sst>
 </file>
@@ -669,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA7DFF8-FE44-4B9E-AF79-499E40D6D221}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
@@ -679,9 +719,9 @@
     <col min="6" max="6" width="36.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="29.9140625" style="2" customWidth="1"/>
     <col min="8" max="8" width="40" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="31.6640625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="54.08203125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="42" style="6" customWidth="1"/>
+    <col min="11" max="11" width="37.5" style="9" customWidth="1"/>
     <col min="12" max="12" width="36.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -710,7 +750,7 @@
       <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>24</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -748,7 +788,7 @@
       <c r="H2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -786,7 +826,7 @@
       <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -824,7 +864,7 @@
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -837,7 +877,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -859,7 +899,7 @@
       <c r="H5" s="2">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J5" s="5" t="s">
@@ -869,7 +909,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -891,20 +931,18 @@
       <c r="H6" s="2">
         <v>2</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="K6" s="7"/>
       <c r="L6" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -926,20 +964,18 @@
       <c r="H7" s="2">
         <v>3</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="K7" s="7"/>
       <c r="L7" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -961,7 +997,7 @@
       <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="5" t="s">
         <v>32</v>
       </c>
       <c r="J8" s="5" t="s">
@@ -972,6 +1008,136 @@
         <v>43</v>
       </c>
     </row>
+    <row r="9" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="2">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2">
+        <v>30</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="2">
+        <v>3</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>201</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="33.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="14" spans="1:12" ht="38" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitProject\REDIV\ReOnline\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2CA86A-DAC7-48CD-A856-515C3AA9C5E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41333CDD-71C1-4508-970E-CBEB07C42BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-12220" yWindow="3600" windowWidth="47520" windowHeight="15840" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="-3330" yWindow="2130" windowWidth="38565" windowHeight="15885" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -152,17 +152,7 @@
     <t>头像-Addressable完整路径</t>
   </si>
   <si>
-    <t>SpineKey</t>
-  </si>
-  <si>
-    <t>战斗Spine-Addressable完整路径</t>
-  </si>
-  <si>
     <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Texture2D/Unit/icon_unit_106011.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Skeleton/Game/106011_SkeletonData.asset</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -261,9 +251,6 @@
     <t>Assets/AddressableAssets/Remote/Character/100001/101/Texture2D/Unit/icon_unit_100261.png</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Skeleton/100211_SkeletonData.asset</t>
-  </si>
-  <si>
     <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Texture2D/CharacterFull/bsm_chara_full_102001_l.png</t>
   </si>
   <si>
@@ -278,13 +265,76 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/100001/102/Prefab/StillUnit/StillUnit_180231.prefab</t>
+  </si>
+  <si>
+    <t>SkeletonUI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkeletonScreen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>UI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>展示预制体</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Spine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="DengXian"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>预制体</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Skeleton/Game/100211_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Skeleton/Game/106011_UI.prefab</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,6 +365,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -709,23 +766,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA7DFF8-FE44-4B9E-AF79-499E40D6D221}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.08203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.875" style="2" customWidth="1"/>
     <col min="5" max="5" width="16" style="2" customWidth="1"/>
-    <col min="6" max="6" width="36.33203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.9140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="36.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="40" style="2" customWidth="1"/>
-    <col min="9" max="9" width="54.08203125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="42" style="6" customWidth="1"/>
-    <col min="11" max="11" width="37.5" style="9" customWidth="1"/>
-    <col min="12" max="12" width="36.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="54.125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="37.5" style="9" customWidth="1"/>
+    <col min="11" max="11" width="36.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="24.75" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -753,17 +811,20 @@
       <c r="I1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>36</v>
+      <c r="J1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -791,17 +852,20 @@
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>37</v>
+      <c r="J2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -829,17 +893,20 @@
       <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>38</v>
+      <c r="J3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="18">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -847,13 +914,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>20</v>
@@ -867,17 +934,20 @@
       <c r="I4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>40</v>
+      <c r="J4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="60">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -900,16 +970,16 @@
         <v>1</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="45">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -932,17 +1002,14 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="9" t="s">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="45">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -965,17 +1032,14 @@
         <v>3</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="9" t="s">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="45">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -998,17 +1062,14 @@
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="9" t="s">
-        <v>43</v>
+      <c r="J8" s="7"/>
+      <c r="K8" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="55.5" customHeight="1">
       <c r="B9" s="2">
         <v>2</v>
       </c>
@@ -1025,22 +1086,22 @@
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>52</v>
+      <c r="L9" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="45.95" customHeight="1">
       <c r="B10" s="2">
         <v>2</v>
       </c>
@@ -1057,22 +1118,19 @@
         <v>15</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2">
         <v>2</v>
       </c>
       <c r="I10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="J10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>53</v>
-      </c>
     </row>
-    <row r="11" spans="1:12" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="48.6" customHeight="1">
       <c r="B11" s="2">
         <v>2</v>
       </c>
@@ -1089,22 +1147,19 @@
         <v>30</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H11" s="2">
         <v>3</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>54</v>
-      </c>
     </row>
-    <row r="12" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="35.1" customHeight="1">
       <c r="B12" s="2">
         <v>2</v>
       </c>
@@ -1127,17 +1182,14 @@
         <v>1</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="L12" s="9" t="s">
-        <v>56</v>
+      <c r="K12" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="33.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:12" ht="38" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:13" ht="33.6" customHeight="1"/>
+    <row r="14" spans="1:13" ht="38.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitProject\REDIV\ReOnline\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41333CDD-71C1-4508-970E-CBEB07C42BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBECB987-228C-4009-AB9F-448237DDDA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3330" yWindow="2130" windowWidth="38565" windowHeight="15885" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="0" yWindow="2205" windowWidth="38565" windowHeight="15885" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -152,29 +152,10 @@
     <t>头像-Addressable完整路径</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Texture2D/Unit/icon_unit_106011.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/Unit/icon_unit_106031.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/Unit/icon_unit_106061.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/202/Texture2D/Unit/icon_unit_180611.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>门槛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Texture2D/CharacterFull/bsm_chara_full_106001_l.png</t>
-  </si>
-  <si>
     <t>StillUnitPrefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,21 +172,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Texture2D/StillUnit/StillUnit106031Preview.prefab</t>
-  </si>
-  <si>
     <t>预览图预制体</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>立绘</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/201/Prefab/StillUnit/StillUnit106031Preview.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/202/Prefab/StillUnit202.prefab</t>
   </si>
   <si>
     <r>
@@ -240,31 +212,6 @@
   <si>
     <t>大天使</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Texture2D/Unit/icon_unit_100211.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/101/Texture2D/Unit/icon_unit_100231.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/101/Texture2D/Unit/icon_unit_100261.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Texture2D/CharacterFull/bsm_chara_full_102001_l.png</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/101/Prefab/StillUnit/StillUnit_101.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/101/Prefab/StillUnit/StillUnit_102.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/102/Texture2D/Unit/icon_unit_180211.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/102/Prefab/StillUnit/StillUnit_180231.prefab</t>
   </si>
   <si>
     <t>SkeletonUI</t>
@@ -324,10 +271,127 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/100001/0Common/Skeleton/Game/100211_UI.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/100002/0Common/Skeleton/Game/106011_UI.prefab</t>
+    <t>Assets/AddressableAssets/Remote/Character/1/0Common/Texture2D/Unit/icon_unit_106011.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/0Common/Texture2D/UnitPlate/unit_plate_106011.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/0Common/Prefab/Skeleton/106011_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Texture2D/Unit/icon_unit_106031.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/StillUnit/StillUnit106031Preview.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/106031_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Texture2D/Unit/icon_unit_106061.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/StillUnit/StillUnit106061Preview.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/106061_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/102/Texture2D/Unit/icon_unit_180611.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/102/Prefab/StillUnit/StillUnit180631.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/102/Prefab/Skeleton/180631_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/0Common/Texture2D/Unit/icon_unit_100211.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/0Common/Texture2D/CharacterFull/bsm_chara_full_102001_l.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/0Common/Prefab/Skeleton/100211_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Texture2D/Unit/icon_unit_100231.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Texture2D/Unit/icon_unit_100261.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/StillUnit/StillUnit_100231.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/StillUnit/StillUnit_100261.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/10231_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/10261_UI.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/202/Texture2D/Unit/icon_unit_180211.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/202/Prefab/StillUnit/StillUnit_180231.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/202/Prefab/Skeleton/18231_UI.prefab</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>略缩图路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Texture2D/UnitPlate/unit_plate_106031.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Texture2D/UnitPlate/unit_plate_106061.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/102/Texture2D/UnitPlate/unit_plate_180631.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/0Common/Texture2D/UnitPlate/unit_plate_100211.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Texture2D/UnitPlate/unit_plate_100231.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Texture2D/UnitPlate/unit_plate_100261.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/202/Texture2D/UnitPlate/unit_plate_180231.png</t>
+  </si>
+  <si>
+    <t>NameIconKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnitPlateIconKey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字图片路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/0Common/Texture2D/Name/chara_name_1078.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/0Common/Texture2D/Name/chara_name_1226.png</t>
   </si>
 </sst>
 </file>
@@ -398,7 +462,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -431,6 +495,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -766,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA7DFF8-FE44-4B9E-AF79-499E40D6D221}">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
@@ -776,14 +843,14 @@
     <col min="6" max="6" width="36.375" style="2" customWidth="1"/>
     <col min="7" max="7" width="29.875" style="2" customWidth="1"/>
     <col min="8" max="8" width="40" style="2" customWidth="1"/>
-    <col min="9" max="9" width="54.125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="37.5" style="9" customWidth="1"/>
-    <col min="11" max="11" width="36.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="24.75" customWidth="1"/>
-    <col min="13" max="13" width="17.125" customWidth="1"/>
+    <col min="9" max="11" width="54.125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="37.5" style="9" customWidth="1"/>
+    <col min="13" max="13" width="36.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="24.75" customWidth="1"/>
+    <col min="15" max="15" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -811,20 +878,26 @@
       <c r="I1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>53</v>
+      <c r="J1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>54</v>
+        <v>27</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -852,20 +925,26 @@
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>34</v>
+      <c r="J2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -893,20 +972,26 @@
       <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
+      <c r="J3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:15" ht="18">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -914,13 +999,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>20</v>
@@ -934,20 +1019,26 @@
       <c r="I4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>56</v>
+      <c r="J4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="60">
+    <row r="5" spans="1:15" ht="60">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -970,16 +1061,22 @@
         <v>1</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>58</v>
+        <v>41</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="45">
+    <row r="6" spans="1:15" ht="60">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -1002,14 +1099,23 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="45">
+    <row r="7" spans="1:15" ht="60">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -1032,14 +1138,23 @@
         <v>3</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="9" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="45">
+    <row r="8" spans="1:15" ht="60">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -1062,14 +1177,23 @@
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="9" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="55.5" customHeight="1">
+    <row r="9" spans="1:15" ht="55.5" customHeight="1">
       <c r="B9" s="2">
         <v>2</v>
       </c>
@@ -1086,22 +1210,28 @@
         <v>0</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="45.95" customHeight="1">
+    <row r="10" spans="1:15" ht="45.95" customHeight="1">
       <c r="B10" s="2">
         <v>2</v>
       </c>
@@ -1118,19 +1248,28 @@
         <v>15</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H10" s="2">
         <v>2</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>49</v>
+        <v>56</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="48.6" customHeight="1">
+    <row r="11" spans="1:15" ht="48.6" customHeight="1">
       <c r="B11" s="2">
         <v>2</v>
       </c>
@@ -1147,19 +1286,28 @@
         <v>30</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2">
         <v>3</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="35.1" customHeight="1">
+    <row r="12" spans="1:15" ht="35.1" customHeight="1">
       <c r="B12" s="2">
         <v>2</v>
       </c>
@@ -1182,14 +1330,23 @@
         <v>1</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>52</v>
+        <v>62</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="33.6" customHeight="1"/>
-    <row r="14" spans="1:13" ht="38.1" customHeight="1"/>
+    <row r="13" spans="1:15" ht="33.6" customHeight="1"/>
+    <row r="14" spans="1:15" ht="38.1" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitProject\REDIV\ReOnline\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBECB987-228C-4009-AB9F-448237DDDA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E64871-D8D6-4672-AC01-FF1BE6D6190F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2205" windowWidth="38565" windowHeight="15885" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="-10050" yWindow="5360" windowWidth="47520" windowHeight="15840" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/2/0Common/Texture2D/Name/chara_name_1226.png</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/0Common/Texture2D/CharacterFull/bsm_chara_full_106001_l.png</t>
   </si>
 </sst>
 </file>
@@ -834,20 +837,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA7DFF8-FE44-4B9E-AF79-499E40D6D221}">
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.08203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16" style="2" customWidth="1"/>
-    <col min="6" max="6" width="36.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="29.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="36.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.83203125" style="2" customWidth="1"/>
     <col min="8" max="8" width="40" style="2" customWidth="1"/>
-    <col min="9" max="11" width="54.125" style="6" customWidth="1"/>
+    <col min="9" max="11" width="54.08203125" style="6" customWidth="1"/>
     <col min="12" max="12" width="37.5" style="9" customWidth="1"/>
     <col min="13" max="13" width="36.75" style="2" customWidth="1"/>
     <col min="14" max="14" width="24.75" customWidth="1"/>
-    <col min="15" max="15" width="17.125" customWidth="1"/>
+    <col min="15" max="15" width="17.08203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -991,7 +994,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18">
+    <row r="4" spans="1:15" ht="18.5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1038,7 +1041,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="60">
+    <row r="5" spans="1:15" ht="58">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1070,13 +1073,13 @@
         <v>78</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="N5" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="60">
+    <row r="6" spans="1:15" ht="58">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -1115,7 +1118,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="60">
+    <row r="7" spans="1:15" ht="58">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -1154,7 +1157,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="60">
+    <row r="8" spans="1:15" ht="58">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -1231,7 +1234,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="45.95" customHeight="1">
+    <row r="10" spans="1:15" ht="46" customHeight="1">
       <c r="B10" s="2">
         <v>2</v>
       </c>
@@ -1269,7 +1272,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="48.6" customHeight="1">
+    <row r="11" spans="1:15" ht="48.65" customHeight="1">
       <c r="B11" s="2">
         <v>2</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="35.1" customHeight="1">
+    <row r="12" spans="1:15" ht="35.15" customHeight="1">
       <c r="B12" s="2">
         <v>2</v>
       </c>
@@ -1345,8 +1348,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="33.6" customHeight="1"/>
-    <row r="14" spans="1:15" ht="38.1" customHeight="1"/>
+    <row r="13" spans="1:15" ht="33.65" customHeight="1"/>
+    <row r="14" spans="1:15" ht="38.15" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E64871-D8D6-4672-AC01-FF1BE6D6190F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E88594A-786A-4087-9B27-F5E769E3B68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10050" yWindow="5360" windowWidth="47520" windowHeight="15840" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="-16620" yWindow="3550" windowWidth="51320" windowHeight="15840" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -395,6 +395,38 @@
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/1/0Common/Texture2D/CharacterFull/bsm_chara_full_106001_l.png</t>
+  </si>
+  <si>
+    <t>SkeletonTown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>城镇控制预制体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/0Common/Prefab/Skeleton/106011_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/1106031_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/1106061_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/102/Prefab/Skeleton/180631_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/0Common/Prefab/Skeleton/100211_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/110231_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/110261_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/202/Prefab/Skeleton/18231_Town.prefab</t>
   </si>
 </sst>
 </file>
@@ -836,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA7DFF8-FE44-4B9E-AF79-499E40D6D221}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="18.25" style="2" customWidth="1"/>
@@ -849,11 +881,11 @@
     <col min="9" max="11" width="54.08203125" style="6" customWidth="1"/>
     <col min="12" max="12" width="37.5" style="9" customWidth="1"/>
     <col min="13" max="13" width="36.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="24.75" customWidth="1"/>
-    <col min="15" max="15" width="17.08203125" customWidth="1"/>
+    <col min="14" max="15" width="24.75" customWidth="1"/>
+    <col min="16" max="16" width="17.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -897,10 +929,13 @@
         <v>37</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -946,8 +981,11 @@
       <c r="O2" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -993,8 +1031,11 @@
       <c r="O3" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="P3" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="18.5">
+    <row r="4" spans="1:16" ht="18.5">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1037,11 +1078,14 @@
       <c r="N4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="58">
+    <row r="5" spans="1:16" ht="58">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1078,8 +1122,11 @@
       <c r="N5" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="O5" s="9" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" ht="58">
+    <row r="6" spans="1:16" ht="58">
       <c r="B6" s="2">
         <v>1</v>
       </c>
@@ -1117,8 +1164,11 @@
       <c r="N6" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="O6" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" ht="58">
+    <row r="7" spans="1:16" ht="58">
       <c r="B7" s="2">
         <v>1</v>
       </c>
@@ -1156,8 +1206,11 @@
       <c r="N7" s="6" t="s">
         <v>49</v>
       </c>
+      <c r="O7" s="6" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" ht="58">
+    <row r="8" spans="1:16" ht="58">
       <c r="B8" s="2">
         <v>1</v>
       </c>
@@ -1195,8 +1248,11 @@
       <c r="N8" s="6" t="s">
         <v>52</v>
       </c>
+      <c r="O8" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" ht="55.5" customHeight="1">
+    <row r="9" spans="1:16" ht="55.5" customHeight="1">
       <c r="B9" s="2">
         <v>2</v>
       </c>
@@ -1233,8 +1289,11 @@
       <c r="N9" s="6" t="s">
         <v>55</v>
       </c>
+      <c r="O9" s="6" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" ht="46" customHeight="1">
+    <row r="10" spans="1:16" ht="46" customHeight="1">
       <c r="B10" s="2">
         <v>2</v>
       </c>
@@ -1271,8 +1330,11 @@
       <c r="N10" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="O10" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" ht="48.65" customHeight="1">
+    <row r="11" spans="1:16" ht="48.65" customHeight="1">
       <c r="B11" s="2">
         <v>2</v>
       </c>
@@ -1309,8 +1371,11 @@
       <c r="N11" s="6" t="s">
         <v>61</v>
       </c>
+      <c r="O11" s="6" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" ht="35.15" customHeight="1">
+    <row r="12" spans="1:16" ht="35.15" customHeight="1">
       <c r="B12" s="2">
         <v>2</v>
       </c>
@@ -1347,9 +1412,12 @@
       <c r="N12" s="9" t="s">
         <v>64</v>
       </c>
+      <c r="O12" s="9" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" ht="33.65" customHeight="1"/>
-    <row r="14" spans="1:15" ht="38.15" customHeight="1"/>
+    <row r="13" spans="1:16" ht="33.65" customHeight="1"/>
+    <row r="14" spans="1:16" ht="38.15" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/CharacterForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E88594A-786A-4087-9B27-F5E769E3B68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409C7838-2463-4386-A062-742A4B70665E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16620" yWindow="3550" windowWidth="51320" windowHeight="15840" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{5FA2398B-8D7C-4AC2-96D7-C9EF3192DA0E}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterForm" sheetId="1" r:id="rId1"/>
@@ -408,25 +408,25 @@
     <t>Assets/AddressableAssets/Remote/Character/1/0Common/Prefab/Skeleton/106011_Town.prefab</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/1106031_Town.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/1106061_Town.prefab</t>
-  </si>
-  <si>
     <t>Assets/AddressableAssets/Remote/Character/1/102/Prefab/Skeleton/180631_Town.prefab</t>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Character/2/0Common/Prefab/Skeleton/100211_Town.prefab</t>
   </si>
   <si>
-    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/110231_Town.prefab</t>
-  </si>
-  <si>
-    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/110261_Town.prefab</t>
-  </si>
-  <si>
     <t>Assets/AddressableAssets/Remote/Character/2/202/Prefab/Skeleton/18231_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/106031_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/1/101/Prefab/Skeleton/106061_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/10231_Town.prefab</t>
+  </si>
+  <si>
+    <t>Assets/AddressableAssets/Remote/Character/2/201/Prefab/Skeleton/10261_Town.prefab</t>
   </si>
 </sst>
 </file>
@@ -1165,7 +1165,7 @@
         <v>46</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="58">
@@ -1207,7 +1207,7 @@
         <v>49</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="58">
@@ -1249,7 +1249,7 @@
         <v>52</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="55.5" customHeight="1">
@@ -1290,10 +1290,10 @@
         <v>55</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="46" customHeight="1">
+    <row r="10" spans="1:16" ht="79" customHeight="1">
       <c r="B10" s="2">
         <v>2</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>60</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="48.65" customHeight="1">
@@ -1372,10 +1372,10 @@
         <v>61</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="35.15" customHeight="1">
+    <row r="12" spans="1:16" ht="75.5" customHeight="1">
       <c r="B12" s="2">
         <v>2</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>64</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="33.65" customHeight="1"/>
